--- a/r4-ELGA-IV-Diabetes-dev2/ValueSet-vs-iv-diagnosekategorie.xlsx
+++ b/r4-ELGA-IV-Diabetes-dev2/ValueSet-vs-iv-diagnosekategorie.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga-iv-diab-r4/ValueSet/vs-iv-diagnosekategorie</t>
+    <t>https://diab.iv.elga.gv.at/ValueSet/vs-iv-diagnosekategorie</t>
   </si>
   <si>
     <t>Version</t>
